--- a/resultados/matriz_clasificacion_porcentajes.xlsx
+++ b/resultados/matriz_clasificacion_porcentajes.xlsx
@@ -436,417 +436,417 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>MAL_MANEJO_CABLES</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MAL_TRATO_FISICO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>MALA_LIMPIEZA_MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>MAL_TRATO_FISICO</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MAL_MANEJO_CABLES</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MONITOR DE SIGNOS VITALES</t>
+          <t xml:space="preserve">NEVERA </t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.31474103585657</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="C2" t="n">
-        <v>6.294820717131475</v>
+        <v>19.14893617021277</v>
       </c>
       <c r="D2" t="n">
-        <v>29.800796812749</v>
+        <v>10.63829787234043</v>
       </c>
       <c r="E2" t="n">
-        <v>52.58964143426294</v>
+        <v>25.53191489361702</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICROSCOPIO </t>
+          <t>INCUBADORA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>22.36842105263158</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66666666666666</v>
+        <v>19.73684210526316</v>
       </c>
       <c r="D3" t="n">
-        <v>8.333333333333332</v>
+        <v>48.68421052631579</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>9.210526315789473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UNIDAD ODONTOLÓGICA</t>
+          <t>TENS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.090909090909092</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>46.75324675324675</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>19.48051948051948</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="E4" t="n">
-        <v>24.67532467532467</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DESFIBRILADOR</t>
+          <t>TERMÓMETRO ELECTRÓNICO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.76470588235294</v>
+        <v>18.86792452830189</v>
       </c>
       <c r="C5" t="n">
-        <v>58.82352941176471</v>
+        <v>16.9811320754717</v>
       </c>
       <c r="D5" t="n">
-        <v>17.64705882352941</v>
+        <v>30.18867924528302</v>
       </c>
       <c r="E5" t="n">
-        <v>11.76470588235294</v>
+        <v>33.9622641509434</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MANTA TÉRMICA</t>
+          <t>TENSIÓMETRO ANEROIDE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.05263157894737</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>26.31578947368421</v>
+        <v>3.703703703703703</v>
       </c>
       <c r="D6" t="n">
-        <v>26.31578947368421</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="E6" t="n">
-        <v>26.31578947368421</v>
+        <v>14.81481481481481</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>TENS</t>
+          <t>MÁQUINA DE ANESTESIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="C7" t="n">
-        <v>11.11111111111111</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="D7" t="n">
-        <v>38.88888888888889</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>30.43478260869566</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>MESA DE CIRUGÍA</t>
+          <t>MANTA TÉRMICA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.76470588235294</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="C8" t="n">
-        <v>5.88235294117647</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="D8" t="n">
-        <v>38.23529411764706</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="E8" t="n">
-        <v>44.11764705882353</v>
+        <v>26.31578947368421</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>INCUBADORA</t>
+          <t>ECOTONE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.36842105263158</v>
+        <v>11.53846153846154</v>
       </c>
       <c r="C9" t="n">
-        <v>9.210526315789473</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="D9" t="n">
-        <v>48.68421052631579</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="E9" t="n">
-        <v>19.73684210526316</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>VENTILADOR ADULTO</t>
+          <t xml:space="preserve">TORRE DE LAPAROSCOPIA </t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64.86486486486487</v>
+        <v>20.75471698113208</v>
       </c>
       <c r="C10" t="n">
-        <v>10.81081081081081</v>
+        <v>45.28301886792453</v>
       </c>
       <c r="D10" t="n">
-        <v>16.21621621621622</v>
+        <v>26.41509433962264</v>
       </c>
       <c r="E10" t="n">
-        <v>8.108108108108109</v>
+        <v>7.547169811320755</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TERMÓMETRO</t>
+          <t>DESFIBRILADOR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22.72727272727273</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="C11" t="n">
-        <v>22.72727272727273</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="D11" t="n">
-        <v>27.27272727272727</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="E11" t="n">
-        <v>27.27272727272727</v>
+        <v>58.82352941176471</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>TERMOHIGRÓMETRO</t>
+          <t>SUPERFICIE DE AIRE ALTERNANTE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.615384615384617</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="C12" t="n">
-        <v>15.38461538461539</v>
+        <v>37.5</v>
       </c>
       <c r="D12" t="n">
-        <v>44.23076923076923</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>30.76923076923077</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>MÁQUINA DE ANESTESIA</t>
+          <t>HUMIDIFICADOR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47.82608695652174</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43478260869566</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="D13" t="n">
-        <v>4.347826086956522</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="E13" t="n">
-        <v>17.39130434782609</v>
+        <v>3.846153846153846</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SUPERFICIE DE AIRE ALTERNANTE</t>
+          <t>ELECTROCARDIÓGRAFO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.333333333333332</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="C14" t="n">
-        <v>12.5</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="D14" t="n">
-        <v>41.66666666666667</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="E14" t="n">
-        <v>37.5</v>
+        <v>10.71428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>TERMÓMETRO DE NEVERA DE TRANSPORTE</t>
+          <t xml:space="preserve">REFRIGERADOR </t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C15" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="D15" t="n">
         <v>16.66666666666666</v>
       </c>
-      <c r="C15" t="n">
-        <v>30</v>
-      </c>
-      <c r="D15" t="n">
-        <v>40</v>
-      </c>
       <c r="E15" t="n">
-        <v>13.33333333333333</v>
+        <v>5.555555555555555</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">INFUSOR </t>
+          <t xml:space="preserve">MICROSCOPIO </t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>ELECTROENCEFALOGRAFO - POLISOMNÓGRAFO</t>
+          <t xml:space="preserve">FLUJÓMETRO </t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>15.09433962264151</v>
       </c>
       <c r="C17" t="n">
-        <v>21.05263157894737</v>
+        <v>11.32075471698113</v>
       </c>
       <c r="D17" t="n">
-        <v>28.94736842105263</v>
+        <v>52.83018867924528</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>20.75471698113208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>BOMBA DE INFUSIÓN</t>
+          <t>TERMÓMETRO DE NEVERA DE TRANSPORTE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>96.29629629629629</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>3.703703703703703</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CENTRAL DE MONITOREO</t>
+          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33.33333333333333</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="C19" t="n">
-        <v>7.407407407407407</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>18.51851851851852</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="E19" t="n">
-        <v>40.74074074074074</v>
+        <v>23.52941176470588</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECÓGRAFO </t>
+          <t>TORRE DE ENDOSCOPIA VIDEOBRONCOSCOPIO VIDEODUODENOSCOPIO VIODEOGASTROSCOPIO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.31578947368421</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>26.31578947368421</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>21.05263157894737</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>26.31578947368421</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>REGULADOR DE VACÍO</t>
+          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO VIDEODUODENO REGULADOR CO2 BOMBA DE IRRIGACIÓN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>14.70588235294118</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>HUMIDIFICADOR</t>
+          <t>VENTILADOR ALTA FRECUENCIA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7.692307692307693</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="C22" t="n">
-        <v>3.846153846153846</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="D22" t="n">
-        <v>34.61538461538461</v>
+        <v>17.14285714285714</v>
       </c>
       <c r="E22" t="n">
-        <v>53.84615384615385</v>
+        <v>8.571428571428571</v>
       </c>
     </row>
     <row r="23">
@@ -859,146 +859,146 @@
         <v>22.22222222222222</v>
       </c>
       <c r="C23" t="n">
-        <v>16.66666666666666</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="D23" t="n">
         <v>38.88888888888889</v>
       </c>
       <c r="E23" t="n">
-        <v>22.22222222222222</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>TENSIÓMETRO ANEROIDE</t>
+          <t>TERMOHIGRÓMETRO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33.33333333333333</v>
+        <v>9.615384615384617</v>
       </c>
       <c r="C24" t="n">
-        <v>14.81481481481481</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="D24" t="n">
-        <v>48.14814814814815</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="E24" t="n">
-        <v>3.703703703703703</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>BÁSCULA DIGITAL</t>
+          <t>MONITOR DE SIGNOS VITALES</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.16666666666667</v>
+        <v>11.31474103585657</v>
       </c>
       <c r="C25" t="n">
-        <v>29.16666666666667</v>
+        <v>52.58964143426294</v>
       </c>
       <c r="D25" t="n">
-        <v>33.33333333333333</v>
+        <v>29.800796812749</v>
       </c>
       <c r="E25" t="n">
-        <v>8.333333333333332</v>
+        <v>6.294820717131475</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>TERMÓMETRO ELECTRÓNICO</t>
+          <t>GENERICO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.86792452830189</v>
+        <v>23.59550561797753</v>
       </c>
       <c r="C26" t="n">
-        <v>33.9622641509434</v>
+        <v>33.70786516853933</v>
       </c>
       <c r="D26" t="n">
-        <v>30.18867924528302</v>
+        <v>30.3370786516854</v>
       </c>
       <c r="E26" t="n">
-        <v>16.9811320754717</v>
+        <v>12.35955056179775</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLUJÓMETRO </t>
+          <t xml:space="preserve">INFUSOR </t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.09433962264151</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>20.75471698113208</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>52.83018867924528</v>
+        <v>76</v>
       </c>
       <c r="E27" t="n">
-        <v>11.32075471698113</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERADOR </t>
+          <t>ELECTROENCEFALOGRAFO - POLISOMNÓGRAFO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>5.555555555555555</v>
+        <v>50</v>
       </c>
       <c r="D28" t="n">
-        <v>16.66666666666666</v>
+        <v>28.94736842105263</v>
       </c>
       <c r="E28" t="n">
-        <v>44.44444444444444</v>
+        <v>21.05263157894737</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELLADORA </t>
+          <t>VENTILADOR ADULTO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.41176470588236</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="C29" t="n">
-        <v>38.82352941176471</v>
+        <v>8.108108108108109</v>
       </c>
       <c r="D29" t="n">
-        <v>22.35294117647059</v>
+        <v>16.21621621621622</v>
       </c>
       <c r="E29" t="n">
-        <v>9.411764705882353</v>
+        <v>10.81081081081081</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>FONENDOSCOPIO</t>
+          <t>CENTRAL DE MONITOREO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13.63636363636363</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>18.18181818181818</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="D30" t="n">
-        <v>59.09090909090909</v>
+        <v>18.51851851851852</v>
       </c>
       <c r="E30" t="n">
-        <v>9.090909090909092</v>
+        <v>7.407407407407407</v>
       </c>
     </row>
     <row r="31">
@@ -1011,181 +1011,181 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C31" t="n">
-        <v>7.142857142857142</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="D31" t="n">
         <v>28.57142857142857</v>
       </c>
       <c r="E31" t="n">
-        <v>57.14285714285714</v>
+        <v>7.142857142857142</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEVERA </t>
+          <t>BOMBA DE INFUSIÓN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44.68085106382978</v>
+        <v>96.29629629629629</v>
       </c>
       <c r="C32" t="n">
-        <v>25.53191489361702</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>10.63829787234043</v>
+        <v>3.703703703703703</v>
       </c>
       <c r="E32" t="n">
-        <v>19.14893617021277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>GENERICO</t>
+          <t>FONENDOSCOPIO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.59550561797753</v>
+        <v>13.63636363636363</v>
       </c>
       <c r="C33" t="n">
-        <v>12.35955056179775</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="D33" t="n">
-        <v>30.3370786516854</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="E33" t="n">
-        <v>33.70786516853933</v>
+        <v>18.18181818181818</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO</t>
+          <t xml:space="preserve">ECÓGRAFO </t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>52.94117647058824</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="C34" t="n">
-        <v>23.52941176470588</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="D34" t="n">
-        <v>23.52941176470588</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>26.31578947368421</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>ELECTROCARDIÓGRAFO</t>
+          <t>CUNA TÉRMICA</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>39.28571428571428</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="C35" t="n">
-        <v>10.71428571428571</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="D35" t="n">
-        <v>21.42857142857143</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="E35" t="n">
-        <v>28.57142857142857</v>
+        <v>10.52631578947368</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>ECOTONE</t>
+          <t>MESA DE CIRUGÍA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11.53846153846154</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="C36" t="n">
-        <v>7.692307692307693</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="D36" t="n">
-        <v>53.84615384615385</v>
+        <v>38.23529411764706</v>
       </c>
       <c r="E36" t="n">
-        <v>26.92307692307692</v>
+        <v>5.88235294117647</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRE DE LAPAROSCOPIA </t>
+          <t>REGULADOR DE VACÍO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.75471698113208</v>
+        <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>7.547169811320755</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>26.41509433962264</v>
+        <v>32</v>
       </c>
       <c r="E37" t="n">
-        <v>45.28301886792453</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO VIDEODUODENO REGULADOR CO2 BOMBA DE IRRIGACIÓN</t>
+          <t>CAMA ELÉCTRICA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>50</v>
+        <v>14.50381679389313</v>
       </c>
       <c r="C38" t="n">
-        <v>14.70588235294118</v>
+        <v>37.40458015267176</v>
       </c>
       <c r="D38" t="n">
-        <v>11.76470588235294</v>
+        <v>41.98473282442748</v>
       </c>
       <c r="E38" t="n">
-        <v>23.52941176470588</v>
+        <v>6.106870229007633</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>VENTILADOR ALTA FRECUENCIA</t>
+          <t>TERMÓMETRO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>42.85714285714285</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="C39" t="n">
-        <v>8.571428571428571</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="D39" t="n">
-        <v>17.14285714285714</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="E39" t="n">
-        <v>31.42857142857143</v>
+        <v>22.72727272727273</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>CUNA TÉRMICA</t>
+          <t>AISLADOR ASÉPTICO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15.78947368421053</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="C40" t="n">
-        <v>10.52631578947368</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="D40" t="n">
-        <v>52.63157894736842</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="E40" t="n">
         <v>21.05263157894737</v>
@@ -1194,58 +1194,58 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>AISLADOR ASÉPTICO</t>
+          <t>UNIDAD ODONTOLÓGICA</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.31578947368421</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="C41" t="n">
-        <v>21.05263157894737</v>
+        <v>24.67532467532467</v>
       </c>
       <c r="D41" t="n">
-        <v>47.36842105263158</v>
+        <v>19.48051948051948</v>
       </c>
       <c r="E41" t="n">
-        <v>5.263157894736842</v>
+        <v>46.75324675324675</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>TORRE DE ENDOSCOPIA VIDEOBRONCOSCOPIO VIDEODUODENOSCOPIO VIODEOGASTROSCOPIO</t>
+          <t xml:space="preserve">SELLADORA </t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.00000000000001</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>9.411764705882353</v>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>22.35294117647059</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>38.82352941176471</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CAMA ELÉCTRICA</t>
+          <t>BÁSCULA DIGITAL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.50381679389313</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="C43" t="n">
-        <v>6.106870229007633</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="D43" t="n">
-        <v>41.98473282442748</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="E43" t="n">
-        <v>37.40458015267176</v>
+        <v>29.16666666666667</v>
       </c>
     </row>
   </sheetData>
